--- a/site/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Candidate Settings</t>
+          <t>Greenhouse Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -925,64 +925,196 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Dayforce Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+          <t>h_01KSFGT62NGMS3DYCB3WB1YB0M</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NGMS3DYCB3WB1YB0M</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Job Configuration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KSFGT62NHYV6F4AH5H5KX2VY</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NHYV6F4AH5H5KX2VY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Job Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KSFGT62NKDZBYYPWWP8K51MD</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NKDZBYYPWWP8K51MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KSFGT62NRE6ZFY3RYC1NHPPT</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NRE6ZFY3RYC1NHPPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Employee Attribute Map</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KSFGT62NPV7A1C9N74RPN023</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NPV7A1C9N74RPN023</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Job Attribute Map</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KSFGT62NXTKQBWNC6SMRV6XJ</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NXTKQBWNC6SMRV6XJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1057,7 +1057,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,54 +1067,76 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/headings.xlsx
@@ -947,7 +947,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Job Configuration</t>
+          <t>Job Management</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Employee Attribute Map</t>
+          <t>Employee Mapper</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Job Attribute Map</t>
+          <t>Job Mapper</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">

--- a/site/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KKGR0E1X2J8YA1DX900C9W7D</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KKGR0E1X2J8YA1DX900C9W7D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,41 +693,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KRDXWM2EN0GY8QKCSWWP3ZQZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KRDXWM2EN0GY8QKCSWWP3ZQZ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KRDXWM2EN0GY8QKCSWWP3ZQZ</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KRDXWM2EN0GY8QKCSWWP3ZQZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Skipped Integration Notification Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,85 +781,85 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Skipped Integration Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>h_01KRDXWM2EG33CBM54TMB99A3W</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KRDXWM2EG33CBM54TMB99A3W</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Analytics Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Candidate Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KRDXWM2EG33CBM54TMB99A3W</t>
+          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KRDXWM2EG33CBM54TMB99A3W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Settings</t>
+          <t>Greenhouse Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,41 +869,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KP5CE7FF276MAFECVTT2A1DN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KP5CE7FF276MAFECVTT2A1DN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Candidate Configuration</t>
+          <t>Dayforce Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>h_01KSFGT62NGMS3DYCB3WB1YB0M</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NGMS3DYCB3WB1YB0M</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Greenhouse Settings</t>
+          <t>PII Fields</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,41 +913,41 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KP5CE7FF276MAFECVTT2A1DN</t>
+          <t>h_01KKGR0E1X2J8YA1DX900C9W7D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KP5CE7FF276MAFECVTT2A1DN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KKGR0E1X2J8YA1DX900C9W7D</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dayforce Settings</t>
+          <t>Job Management</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KSFGT62NGMS3DYCB3WB1YB0M</t>
+          <t>h_01KSFGT62NHYV6F4AH5H5KX2VY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NGMS3DYCB3WB1YB0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NHYV6F4AH5H5KX2VY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Job Management</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,19 +957,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KSFGT62NHYV6F4AH5H5KX2VY</t>
+          <t>h_01KSFGT62NRE6ZFY3RYC1NHPPT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NHYV6F4AH5H5KX2VY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NRE6ZFY3RYC1NHPPT</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Job Settings</t>
+          <t>Employee Mapper</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,164 +979,120 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KSFGT62NKDZBYYPWWP8K51MD</t>
+          <t>h_01KSFGT62NPV7A1C9N74RPN023</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NKDZBYYPWWP8K51MD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NPV7A1C9N74RPN023</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Job Mapper</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KSFGT62NRE6ZFY3RYC1NHPPT</t>
+          <t>h_01KSFGT62NXTKQBWNC6SMRV6XJ</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NRE6ZFY3RYC1NHPPT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NXTKQBWNC6SMRV6XJ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Employee Mapper</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KSFGT62NPV7A1C9N74RPN023</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NPV7A1C9N74RPN023</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Job Mapper</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KSFGT62NXTKQBWNC6SMRV6XJ</t>
+          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KSFGT62NXTKQBWNC6SMRV6XJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Recruiting-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
